--- a/uid/103A机房建模信息整理.xlsx
+++ b/uid/103A机房建模信息整理.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="末端空调" sheetId="1" r:id="rId1"/>
     <sheet name="冷冻水" sheetId="2" r:id="rId2"/>
     <sheet name="列头柜" sheetId="3" r:id="rId3"/>
+    <sheet name="温湿度计" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="354">
   <si>
     <t>设备名称</t>
   </si>
@@ -782,6 +783,315 @@
   </si>
   <si>
     <t>N2_S0_E181_A7</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道33#温湿度</t>
+  </si>
+  <si>
+    <t>1#温度</t>
+  </si>
+  <si>
+    <t>a7217828_ed16_4ffa_b789_04ada92a2e75</t>
+  </si>
+  <si>
+    <t>1#湿度</t>
+  </si>
+  <si>
+    <t>52664cb3_a254_46c0_9674_777ef3b68793</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道32#温湿度</t>
+  </si>
+  <si>
+    <t>a38944a0_b951_45b2_a13c_13a6fa9223e4</t>
+  </si>
+  <si>
+    <t>600edf85_f3ec_46e5_a811_855f82ae07f4</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道31#温湿度</t>
+  </si>
+  <si>
+    <t>4fe07996_cd59_4771_ab80_bab15210849b</t>
+  </si>
+  <si>
+    <t>b111676c_bfed_4fca_a23e_91774e9736fa</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道30#温湿度</t>
+  </si>
+  <si>
+    <t>44686a4e_336a_471f_9f04_abfe29f12c8a</t>
+  </si>
+  <si>
+    <t>24e69074_556e_421e_88bc_d983f21e2a46</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道29#温湿度</t>
+  </si>
+  <si>
+    <t>0ab54859_d564_4e3d_9810_2d74a26d007d</t>
+  </si>
+  <si>
+    <t>25c42ff2_2278_42ca_b97c_43f82cf29737</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道28#温湿度</t>
+  </si>
+  <si>
+    <t>f50dd4c9_c782_4c40_81e6_14dcfd755436</t>
+  </si>
+  <si>
+    <t>dd6f7451_7a3d_4656_97ef_b350af38491a</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道27#温湿度</t>
+  </si>
+  <si>
+    <t>bdb38c2a_f0c6_49c0_b62a_d4e0fc5fd0ea</t>
+  </si>
+  <si>
+    <t>b3582d8f_390a_4db6_8f42_68be2cad1339</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道26#温湿度</t>
+  </si>
+  <si>
+    <t>a10310ed_ff3a_4bdf_b02e_0362f5808958</t>
+  </si>
+  <si>
+    <t>0dc718ed_ea4c_4d82_be43_6d94b9943fa7</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道25#温湿度</t>
+  </si>
+  <si>
+    <t>07bb7d1d_b635_4ca9_909c_7bdaf3ceab10</t>
+  </si>
+  <si>
+    <t>e8700958_d7b7_4050_874d_294fbe149531</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道24#温湿度</t>
+  </si>
+  <si>
+    <t>be578260_b5e1_4e29_888f_4ba9d2c1b138</t>
+  </si>
+  <si>
+    <t>8e318fc0_0003_43c3_8817_0920307d4e1a</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道23#温湿度</t>
+  </si>
+  <si>
+    <t>ad0a96f7_8d56_4120_b0fd_666f6419da54</t>
+  </si>
+  <si>
+    <t>50811f02_536c_4bdb_88f7_1769d6110ea1</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道22#温湿度</t>
+  </si>
+  <si>
+    <t>温度</t>
+  </si>
+  <si>
+    <t>N2_S0_E102_A1</t>
+  </si>
+  <si>
+    <t>湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E102_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道21#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E101_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E101_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道20#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E100_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E100_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道19#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E99_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E99_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道18#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E98_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E98_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道17#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E97_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E97_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道16#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E96_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E96_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道15#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E95_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E95_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道14#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E94_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E94_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道13#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E93_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E93_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道12#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E92_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E92_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道11#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E91_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E91_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道10#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E90_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E90_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道9#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E89_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E89_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道8#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E88_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E88_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道7#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E87_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E87_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道6#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E86_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E86_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道5#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E85_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E85_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道4#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E84_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E84_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房冷通道3#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E83_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E83_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道2#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E82_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E82_A2</t>
+  </si>
+  <si>
+    <t>1F IDC机房热通道1#温湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E81_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E81_A2</t>
   </si>
 </sst>
 </file>
@@ -1404,13 +1714,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1806,34 +2116,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
+      <c r="J2" s="1"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -1843,40 +2153,40 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="3"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="3"/>
+      <c r="J3" s="1"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -1886,40 +2196,40 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
+      <c r="J4" s="1"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1931,40 +2241,40 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="3"/>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="3"/>
-      <c r="AN4" s="3"/>
-      <c r="AO4" s="3"/>
-      <c r="AP4" s="3"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+      <c r="AP4" s="1"/>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="1"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1976,40 +2286,40 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="3"/>
-      <c r="AP5" s="3"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="1"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -2021,40 +2331,40 @@
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-      <c r="AO6" s="3"/>
-      <c r="AP6" s="3"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="1"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -2066,40 +2376,40 @@
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="3"/>
-      <c r="AI7" s="3"/>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
-      <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
-      <c r="AO7" s="3"/>
-      <c r="AP7" s="3"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
     </row>
     <row r="8" spans="1:42">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="1"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -2111,40 +2421,40 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="3"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="3"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="1"/>
+      <c r="AP8" s="1"/>
     </row>
     <row r="9" spans="1:42">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="3"/>
+      <c r="J9" s="1"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -2156,40 +2466,40 @@
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="3"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+      <c r="AO9" s="1"/>
+      <c r="AP9" s="1"/>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="3"/>
+      <c r="J10" s="1"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -2201,40 +2511,40 @@
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="3"/>
-      <c r="AH10" s="3"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="3"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="1"/>
+      <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="1"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -2246,40 +2556,40 @@
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+      <c r="AL11" s="1"/>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+      <c r="AO11" s="1"/>
+      <c r="AP11" s="1"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="1"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -2291,40 +2601,40 @@
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="3"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="1"/>
+      <c r="AP12" s="1"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="1"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2336,40 +2646,40 @@
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="1"/>
+      <c r="AO13" s="1"/>
+      <c r="AP13" s="1"/>
     </row>
     <row r="14" spans="1:42">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="1"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2381,40 +2691,40 @@
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="3"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+      <c r="AP14" s="1"/>
     </row>
     <row r="15" spans="1:42">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="1"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2426,40 +2736,40 @@
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="3"/>
-      <c r="AH15" s="3"/>
-      <c r="AI15" s="3"/>
-      <c r="AJ15" s="3"/>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="3"/>
-      <c r="AM15" s="3"/>
-      <c r="AN15" s="3"/>
-      <c r="AO15" s="3"/>
-      <c r="AP15" s="3"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+      <c r="AO15" s="1"/>
+      <c r="AP15" s="1"/>
     </row>
     <row r="16" spans="1:42">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="1"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2471,40 +2781,40 @@
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3"/>
-      <c r="AG16" s="3"/>
-      <c r="AH16" s="3"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3"/>
-      <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+      <c r="AO16" s="1"/>
+      <c r="AP16" s="1"/>
     </row>
     <row r="17" spans="1:42">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="1"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2516,40 +2826,40 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="3"/>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
-      <c r="AJ17" s="3"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="3"/>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="3"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+      <c r="AP17" s="1"/>
     </row>
     <row r="18" spans="1:42">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2561,40 +2871,40 @@
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="3"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
-      <c r="AJ18" s="3"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="3"/>
-      <c r="AM18" s="3"/>
-      <c r="AN18" s="3"/>
-      <c r="AO18" s="3"/>
-      <c r="AP18" s="3"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="1"/>
+      <c r="AN18" s="1"/>
+      <c r="AO18" s="1"/>
+      <c r="AP18" s="1"/>
     </row>
     <row r="19" spans="1:42">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="1"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2606,40 +2916,40 @@
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="3"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
     </row>
     <row r="20" spans="1:42">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="1"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2651,40 +2961,40 @@
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="3"/>
-      <c r="AF20" s="3"/>
-      <c r="AG20" s="3"/>
-      <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
-      <c r="AJ20" s="3"/>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3"/>
-      <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
-      <c r="AO20" s="3"/>
-      <c r="AP20" s="3"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
     </row>
     <row r="21" spans="1:42">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
+      <c r="J21" s="1"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2696,40 +3006,40 @@
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="3"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="3"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
+      <c r="AM21" s="1"/>
+      <c r="AN21" s="1"/>
+      <c r="AO21" s="1"/>
+      <c r="AP21" s="1"/>
     </row>
     <row r="22" spans="1:42">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="1"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -2741,40 +3051,40 @@
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="3"/>
-      <c r="AG22" s="3"/>
-      <c r="AH22" s="3"/>
-      <c r="AI22" s="3"/>
-      <c r="AJ22" s="3"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="3"/>
-      <c r="AM22" s="3"/>
-      <c r="AN22" s="3"/>
-      <c r="AO22" s="3"/>
-      <c r="AP22" s="3"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
+      <c r="AI22" s="1"/>
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="1"/>
+      <c r="AM22" s="1"/>
+      <c r="AN22" s="1"/>
+      <c r="AO22" s="1"/>
+      <c r="AP22" s="1"/>
     </row>
     <row r="23" spans="1:42">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
+      <c r="J23" s="1"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -2786,40 +3096,40 @@
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
-      <c r="AE23" s="3"/>
-      <c r="AF23" s="3"/>
-      <c r="AG23" s="3"/>
-      <c r="AH23" s="3"/>
-      <c r="AI23" s="3"/>
-      <c r="AJ23" s="3"/>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="3"/>
-      <c r="AM23" s="3"/>
-      <c r="AN23" s="3"/>
-      <c r="AO23" s="3"/>
-      <c r="AP23" s="3"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+      <c r="AI23" s="1"/>
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="1"/>
+      <c r="AM23" s="1"/>
+      <c r="AN23" s="1"/>
+      <c r="AO23" s="1"/>
+      <c r="AP23" s="1"/>
     </row>
     <row r="24" spans="1:42">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
+      <c r="J24" s="1"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2831,40 +3141,40 @@
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
-      <c r="AF24" s="3"/>
-      <c r="AG24" s="3"/>
-      <c r="AH24" s="3"/>
-      <c r="AI24" s="3"/>
-      <c r="AJ24" s="3"/>
-      <c r="AK24" s="3"/>
-      <c r="AL24" s="3"/>
-      <c r="AM24" s="3"/>
-      <c r="AN24" s="3"/>
-      <c r="AO24" s="3"/>
-      <c r="AP24" s="3"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+      <c r="AO24" s="1"/>
+      <c r="AP24" s="1"/>
     </row>
     <row r="25" spans="1:42">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
+      <c r="J25" s="1"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2876,40 +3186,40 @@
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="3"/>
-      <c r="AH25" s="3"/>
-      <c r="AI25" s="3"/>
-      <c r="AJ25" s="3"/>
-      <c r="AK25" s="3"/>
-      <c r="AL25" s="3"/>
-      <c r="AM25" s="3"/>
-      <c r="AN25" s="3"/>
-      <c r="AO25" s="3"/>
-      <c r="AP25" s="3"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="1"/>
+      <c r="AM25" s="1"/>
+      <c r="AN25" s="1"/>
+      <c r="AO25" s="1"/>
+      <c r="AP25" s="1"/>
     </row>
     <row r="26" spans="1:41">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
+      <c r="J26" s="1"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2921,39 +3231,39 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
-      <c r="AB26" s="3"/>
-      <c r="AC26" s="3"/>
-      <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
-      <c r="AF26" s="3"/>
-      <c r="AG26" s="3"/>
-      <c r="AH26" s="3"/>
-      <c r="AI26" s="3"/>
-      <c r="AJ26" s="3"/>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-      <c r="AM26" s="3"/>
-      <c r="AN26" s="3"/>
-      <c r="AO26" s="3"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="1"/>
     </row>
     <row r="27" spans="1:41">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="1"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2965,39 +3275,39 @@
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
-      <c r="AE27" s="3"/>
-      <c r="AF27" s="3"/>
-      <c r="AG27" s="3"/>
-      <c r="AH27" s="3"/>
-      <c r="AI27" s="3"/>
-      <c r="AJ27" s="3"/>
-      <c r="AK27" s="3"/>
-      <c r="AL27" s="3"/>
-      <c r="AM27" s="3"/>
-      <c r="AN27" s="3"/>
-      <c r="AO27" s="3"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+      <c r="AO27" s="1"/>
     </row>
     <row r="28" spans="1:41">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="3"/>
+      <c r="J28" s="1"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -3009,39 +3319,39 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
-      <c r="AF28" s="3"/>
-      <c r="AG28" s="3"/>
-      <c r="AH28" s="3"/>
-      <c r="AI28" s="3"/>
-      <c r="AJ28" s="3"/>
-      <c r="AK28" s="3"/>
-      <c r="AL28" s="3"/>
-      <c r="AM28" s="3"/>
-      <c r="AN28" s="3"/>
-      <c r="AO28" s="3"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="1"/>
+      <c r="AO28" s="1"/>
     </row>
     <row r="29" spans="1:41">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="3"/>
+      <c r="J29" s="1"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -3053,39 +3363,39 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
-      <c r="AB29" s="3"/>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="3"/>
-      <c r="AE29" s="3"/>
-      <c r="AF29" s="3"/>
-      <c r="AG29" s="3"/>
-      <c r="AH29" s="3"/>
-      <c r="AI29" s="3"/>
-      <c r="AJ29" s="3"/>
-      <c r="AK29" s="3"/>
-      <c r="AL29" s="3"/>
-      <c r="AM29" s="3"/>
-      <c r="AN29" s="3"/>
-      <c r="AO29" s="3"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+      <c r="AO29" s="1"/>
     </row>
     <row r="30" spans="1:41">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="3"/>
+      <c r="J30" s="1"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -3097,39 +3407,39 @@
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3"/>
-      <c r="AB30" s="3"/>
-      <c r="AC30" s="3"/>
-      <c r="AD30" s="3"/>
-      <c r="AE30" s="3"/>
-      <c r="AF30" s="3"/>
-      <c r="AG30" s="3"/>
-      <c r="AH30" s="3"/>
-      <c r="AI30" s="3"/>
-      <c r="AJ30" s="3"/>
-      <c r="AK30" s="3"/>
-      <c r="AL30" s="3"/>
-      <c r="AM30" s="3"/>
-      <c r="AN30" s="3"/>
-      <c r="AO30" s="3"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1"/>
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="1"/>
+      <c r="AO30" s="1"/>
     </row>
     <row r="31" spans="1:41">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="3"/>
+      <c r="J31" s="1"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -3141,39 +3451,39 @@
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="3"/>
-      <c r="AB31" s="3"/>
-      <c r="AC31" s="3"/>
-      <c r="AD31" s="3"/>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="3"/>
-      <c r="AG31" s="3"/>
-      <c r="AH31" s="3"/>
-      <c r="AI31" s="3"/>
-      <c r="AJ31" s="3"/>
-      <c r="AK31" s="3"/>
-      <c r="AL31" s="3"/>
-      <c r="AM31" s="3"/>
-      <c r="AN31" s="3"/>
-      <c r="AO31" s="3"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+      <c r="AO31" s="1"/>
     </row>
     <row r="32" spans="1:41">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -3185,39 +3495,39 @@
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="3"/>
-      <c r="AC32" s="3"/>
-      <c r="AD32" s="3"/>
-      <c r="AE32" s="3"/>
-      <c r="AF32" s="3"/>
-      <c r="AG32" s="3"/>
-      <c r="AH32" s="3"/>
-      <c r="AI32" s="3"/>
-      <c r="AJ32" s="3"/>
-      <c r="AK32" s="3"/>
-      <c r="AL32" s="3"/>
-      <c r="AM32" s="3"/>
-      <c r="AN32" s="3"/>
-      <c r="AO32" s="3"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+      <c r="AO32" s="1"/>
     </row>
     <row r="33" spans="1:41">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="3"/>
+      <c r="J33" s="1"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -3229,39 +3539,39 @@
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="3"/>
-      <c r="AC33" s="3"/>
-      <c r="AD33" s="3"/>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="3"/>
-      <c r="AG33" s="3"/>
-      <c r="AH33" s="3"/>
-      <c r="AI33" s="3"/>
-      <c r="AJ33" s="3"/>
-      <c r="AK33" s="3"/>
-      <c r="AL33" s="3"/>
-      <c r="AM33" s="3"/>
-      <c r="AN33" s="3"/>
-      <c r="AO33" s="3"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
+      <c r="AM33" s="1"/>
+      <c r="AN33" s="1"/>
+      <c r="AO33" s="1"/>
     </row>
     <row r="34" spans="1:41">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="3"/>
+      <c r="J34" s="1"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -3273,39 +3583,39 @@
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="3"/>
-      <c r="AC34" s="3"/>
-      <c r="AD34" s="3"/>
-      <c r="AE34" s="3"/>
-      <c r="AF34" s="3"/>
-      <c r="AG34" s="3"/>
-      <c r="AH34" s="3"/>
-      <c r="AI34" s="3"/>
-      <c r="AJ34" s="3"/>
-      <c r="AK34" s="3"/>
-      <c r="AL34" s="3"/>
-      <c r="AM34" s="3"/>
-      <c r="AN34" s="3"/>
-      <c r="AO34" s="3"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1"/>
+      <c r="AO34" s="1"/>
     </row>
     <row r="35" spans="1:41">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="3"/>
+      <c r="J35" s="1"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -3317,39 +3627,39 @@
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
       <c r="Y35" s="2"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3"/>
-      <c r="AB35" s="3"/>
-      <c r="AC35" s="3"/>
-      <c r="AD35" s="3"/>
-      <c r="AE35" s="3"/>
-      <c r="AF35" s="3"/>
-      <c r="AG35" s="3"/>
-      <c r="AH35" s="3"/>
-      <c r="AI35" s="3"/>
-      <c r="AJ35" s="3"/>
-      <c r="AK35" s="3"/>
-      <c r="AL35" s="3"/>
-      <c r="AM35" s="3"/>
-      <c r="AN35" s="3"/>
-      <c r="AO35" s="3"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="1"/>
+      <c r="AO35" s="1"/>
     </row>
     <row r="36" spans="1:41">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="3"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -3361,39 +3671,39 @@
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="2"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3"/>
-      <c r="AB36" s="3"/>
-      <c r="AC36" s="3"/>
-      <c r="AD36" s="3"/>
-      <c r="AE36" s="3"/>
-      <c r="AF36" s="3"/>
-      <c r="AG36" s="3"/>
-      <c r="AH36" s="3"/>
-      <c r="AI36" s="3"/>
-      <c r="AJ36" s="3"/>
-      <c r="AK36" s="3"/>
-      <c r="AL36" s="3"/>
-      <c r="AM36" s="3"/>
-      <c r="AN36" s="3"/>
-      <c r="AO36" s="3"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+      <c r="AI36" s="1"/>
+      <c r="AJ36" s="1"/>
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="1"/>
+      <c r="AM36" s="1"/>
+      <c r="AN36" s="1"/>
+      <c r="AO36" s="1"/>
     </row>
     <row r="37" spans="1:41">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="3"/>
+      <c r="J37" s="1"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -3405,39 +3715,39 @@
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
       <c r="Y37" s="2"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3"/>
-      <c r="AB37" s="3"/>
-      <c r="AC37" s="3"/>
-      <c r="AD37" s="3"/>
-      <c r="AE37" s="3"/>
-      <c r="AF37" s="3"/>
-      <c r="AG37" s="3"/>
-      <c r="AH37" s="3"/>
-      <c r="AI37" s="3"/>
-      <c r="AJ37" s="3"/>
-      <c r="AK37" s="3"/>
-      <c r="AL37" s="3"/>
-      <c r="AM37" s="3"/>
-      <c r="AN37" s="3"/>
-      <c r="AO37" s="3"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+      <c r="AI37" s="1"/>
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="1"/>
+      <c r="AM37" s="1"/>
+      <c r="AN37" s="1"/>
+      <c r="AO37" s="1"/>
     </row>
     <row r="38" spans="1:41">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="3"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -3449,39 +3759,39 @@
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="2"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3"/>
-      <c r="AC38" s="3"/>
-      <c r="AD38" s="3"/>
-      <c r="AE38" s="3"/>
-      <c r="AF38" s="3"/>
-      <c r="AG38" s="3"/>
-      <c r="AH38" s="3"/>
-      <c r="AI38" s="3"/>
-      <c r="AJ38" s="3"/>
-      <c r="AK38" s="3"/>
-      <c r="AL38" s="3"/>
-      <c r="AM38" s="3"/>
-      <c r="AN38" s="3"/>
-      <c r="AO38" s="3"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+      <c r="AG38" s="1"/>
+      <c r="AH38" s="1"/>
+      <c r="AI38" s="1"/>
+      <c r="AJ38" s="1"/>
+      <c r="AK38" s="1"/>
+      <c r="AL38" s="1"/>
+      <c r="AM38" s="1"/>
+      <c r="AN38" s="1"/>
+      <c r="AO38" s="1"/>
     </row>
     <row r="39" spans="1:41">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="3"/>
+      <c r="J39" s="1"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -3493,39 +3803,39 @@
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
       <c r="Y39" s="2"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
-      <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="3"/>
-      <c r="AG39" s="3"/>
-      <c r="AH39" s="3"/>
-      <c r="AI39" s="3"/>
-      <c r="AJ39" s="3"/>
-      <c r="AK39" s="3"/>
-      <c r="AL39" s="3"/>
-      <c r="AM39" s="3"/>
-      <c r="AN39" s="3"/>
-      <c r="AO39" s="3"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+      <c r="AG39" s="1"/>
+      <c r="AH39" s="1"/>
+      <c r="AI39" s="1"/>
+      <c r="AJ39" s="1"/>
+      <c r="AK39" s="1"/>
+      <c r="AL39" s="1"/>
+      <c r="AM39" s="1"/>
+      <c r="AN39" s="1"/>
+      <c r="AO39" s="1"/>
     </row>
     <row r="40" spans="1:41">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="3"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -3537,39 +3847,39 @@
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="2"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
-      <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
-      <c r="AE40" s="3"/>
-      <c r="AF40" s="3"/>
-      <c r="AG40" s="3"/>
-      <c r="AH40" s="3"/>
-      <c r="AI40" s="3"/>
-      <c r="AJ40" s="3"/>
-      <c r="AK40" s="3"/>
-      <c r="AL40" s="3"/>
-      <c r="AM40" s="3"/>
-      <c r="AN40" s="3"/>
-      <c r="AO40" s="3"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+      <c r="AG40" s="1"/>
+      <c r="AH40" s="1"/>
+      <c r="AI40" s="1"/>
+      <c r="AJ40" s="1"/>
+      <c r="AK40" s="1"/>
+      <c r="AL40" s="1"/>
+      <c r="AM40" s="1"/>
+      <c r="AN40" s="1"/>
+      <c r="AO40" s="1"/>
     </row>
     <row r="41" spans="1:41">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="3"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -3581,39 +3891,39 @@
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
       <c r="Y41" s="2"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
-      <c r="AB41" s="3"/>
-      <c r="AC41" s="3"/>
-      <c r="AD41" s="3"/>
-      <c r="AE41" s="3"/>
-      <c r="AF41" s="3"/>
-      <c r="AG41" s="3"/>
-      <c r="AH41" s="3"/>
-      <c r="AI41" s="3"/>
-      <c r="AJ41" s="3"/>
-      <c r="AK41" s="3"/>
-      <c r="AL41" s="3"/>
-      <c r="AM41" s="3"/>
-      <c r="AN41" s="3"/>
-      <c r="AO41" s="3"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+      <c r="AG41" s="1"/>
+      <c r="AH41" s="1"/>
+      <c r="AI41" s="1"/>
+      <c r="AJ41" s="1"/>
+      <c r="AK41" s="1"/>
+      <c r="AL41" s="1"/>
+      <c r="AM41" s="1"/>
+      <c r="AN41" s="1"/>
+      <c r="AO41" s="1"/>
     </row>
     <row r="42" spans="1:41">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="3"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -3625,39 +3935,39 @@
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
       <c r="Y42" s="2"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AC42" s="3"/>
-      <c r="AD42" s="3"/>
-      <c r="AE42" s="3"/>
-      <c r="AF42" s="3"/>
-      <c r="AG42" s="3"/>
-      <c r="AH42" s="3"/>
-      <c r="AI42" s="3"/>
-      <c r="AJ42" s="3"/>
-      <c r="AK42" s="3"/>
-      <c r="AL42" s="3"/>
-      <c r="AM42" s="3"/>
-      <c r="AN42" s="3"/>
-      <c r="AO42" s="3"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+      <c r="AL42" s="1"/>
+      <c r="AM42" s="1"/>
+      <c r="AN42" s="1"/>
+      <c r="AO42" s="1"/>
     </row>
     <row r="43" spans="1:41">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="3"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -3669,39 +3979,39 @@
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
       <c r="Y43" s="2"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="3"/>
-      <c r="AB43" s="3"/>
-      <c r="AC43" s="3"/>
-      <c r="AD43" s="3"/>
-      <c r="AE43" s="3"/>
-      <c r="AF43" s="3"/>
-      <c r="AG43" s="3"/>
-      <c r="AH43" s="3"/>
-      <c r="AI43" s="3"/>
-      <c r="AJ43" s="3"/>
-      <c r="AK43" s="3"/>
-      <c r="AL43" s="3"/>
-      <c r="AM43" s="3"/>
-      <c r="AN43" s="3"/>
-      <c r="AO43" s="3"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AI43" s="1"/>
+      <c r="AJ43" s="1"/>
+      <c r="AK43" s="1"/>
+      <c r="AL43" s="1"/>
+      <c r="AM43" s="1"/>
+      <c r="AN43" s="1"/>
+      <c r="AO43" s="1"/>
     </row>
     <row r="44" spans="1:41">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="3"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -3713,39 +4023,39 @@
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
-      <c r="AB44" s="3"/>
-      <c r="AC44" s="3"/>
-      <c r="AD44" s="3"/>
-      <c r="AE44" s="3"/>
-      <c r="AF44" s="3"/>
-      <c r="AG44" s="3"/>
-      <c r="AH44" s="3"/>
-      <c r="AI44" s="3"/>
-      <c r="AJ44" s="3"/>
-      <c r="AK44" s="3"/>
-      <c r="AL44" s="3"/>
-      <c r="AM44" s="3"/>
-      <c r="AN44" s="3"/>
-      <c r="AO44" s="3"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="1"/>
+      <c r="AM44" s="1"/>
+      <c r="AN44" s="1"/>
+      <c r="AO44" s="1"/>
     </row>
     <row r="45" spans="1:41">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="3"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -3757,39 +4067,39 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
       <c r="Y45" s="2"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="3"/>
-      <c r="AB45" s="3"/>
-      <c r="AC45" s="3"/>
-      <c r="AD45" s="3"/>
-      <c r="AE45" s="3"/>
-      <c r="AF45" s="3"/>
-      <c r="AG45" s="3"/>
-      <c r="AH45" s="3"/>
-      <c r="AI45" s="3"/>
-      <c r="AJ45" s="3"/>
-      <c r="AK45" s="3"/>
-      <c r="AL45" s="3"/>
-      <c r="AM45" s="3"/>
-      <c r="AN45" s="3"/>
-      <c r="AO45" s="3"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+      <c r="AG45" s="1"/>
+      <c r="AH45" s="1"/>
+      <c r="AI45" s="1"/>
+      <c r="AJ45" s="1"/>
+      <c r="AK45" s="1"/>
+      <c r="AL45" s="1"/>
+      <c r="AM45" s="1"/>
+      <c r="AN45" s="1"/>
+      <c r="AO45" s="1"/>
     </row>
     <row r="46" spans="1:41">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="3"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -3801,39 +4111,39 @@
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
       <c r="Y46" s="2"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
-      <c r="AB46" s="3"/>
-      <c r="AC46" s="3"/>
-      <c r="AD46" s="3"/>
-      <c r="AE46" s="3"/>
-      <c r="AF46" s="3"/>
-      <c r="AG46" s="3"/>
-      <c r="AH46" s="3"/>
-      <c r="AI46" s="3"/>
-      <c r="AJ46" s="3"/>
-      <c r="AK46" s="3"/>
-      <c r="AL46" s="3"/>
-      <c r="AM46" s="3"/>
-      <c r="AN46" s="3"/>
-      <c r="AO46" s="3"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AH46" s="1"/>
+      <c r="AI46" s="1"/>
+      <c r="AJ46" s="1"/>
+      <c r="AK46" s="1"/>
+      <c r="AL46" s="1"/>
+      <c r="AM46" s="1"/>
+      <c r="AN46" s="1"/>
+      <c r="AO46" s="1"/>
     </row>
     <row r="47" spans="1:41">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="3"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -3845,39 +4155,39 @@
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
       <c r="Y47" s="2"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
-      <c r="AB47" s="3"/>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3"/>
-      <c r="AG47" s="3"/>
-      <c r="AH47" s="3"/>
-      <c r="AI47" s="3"/>
-      <c r="AJ47" s="3"/>
-      <c r="AK47" s="3"/>
-      <c r="AL47" s="3"/>
-      <c r="AM47" s="3"/>
-      <c r="AN47" s="3"/>
-      <c r="AO47" s="3"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AH47" s="1"/>
+      <c r="AI47" s="1"/>
+      <c r="AJ47" s="1"/>
+      <c r="AK47" s="1"/>
+      <c r="AL47" s="1"/>
+      <c r="AM47" s="1"/>
+      <c r="AN47" s="1"/>
+      <c r="AO47" s="1"/>
     </row>
     <row r="48" spans="1:41">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="3"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -3889,39 +4199,39 @@
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
       <c r="Y48" s="2"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
-      <c r="AB48" s="3"/>
-      <c r="AC48" s="3"/>
-      <c r="AD48" s="3"/>
-      <c r="AE48" s="3"/>
-      <c r="AF48" s="3"/>
-      <c r="AG48" s="3"/>
-      <c r="AH48" s="3"/>
-      <c r="AI48" s="3"/>
-      <c r="AJ48" s="3"/>
-      <c r="AK48" s="3"/>
-      <c r="AL48" s="3"/>
-      <c r="AM48" s="3"/>
-      <c r="AN48" s="3"/>
-      <c r="AO48" s="3"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AH48" s="1"/>
+      <c r="AI48" s="1"/>
+      <c r="AJ48" s="1"/>
+      <c r="AK48" s="1"/>
+      <c r="AL48" s="1"/>
+      <c r="AM48" s="1"/>
+      <c r="AN48" s="1"/>
+      <c r="AO48" s="1"/>
     </row>
     <row r="49" spans="1:41">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="3"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -3933,39 +4243,39 @@
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
       <c r="Y49" s="2"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="3"/>
-      <c r="AB49" s="3"/>
-      <c r="AC49" s="3"/>
-      <c r="AD49" s="3"/>
-      <c r="AE49" s="3"/>
-      <c r="AF49" s="3"/>
-      <c r="AG49" s="3"/>
-      <c r="AH49" s="3"/>
-      <c r="AI49" s="3"/>
-      <c r="AJ49" s="3"/>
-      <c r="AK49" s="3"/>
-      <c r="AL49" s="3"/>
-      <c r="AM49" s="3"/>
-      <c r="AN49" s="3"/>
-      <c r="AO49" s="3"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="1"/>
+      <c r="AD49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1"/>
+      <c r="AG49" s="1"/>
+      <c r="AH49" s="1"/>
+      <c r="AI49" s="1"/>
+      <c r="AJ49" s="1"/>
+      <c r="AK49" s="1"/>
+      <c r="AL49" s="1"/>
+      <c r="AM49" s="1"/>
+      <c r="AN49" s="1"/>
+      <c r="AO49" s="1"/>
     </row>
     <row r="50" spans="1:41">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="3"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -3977,39 +4287,39 @@
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
       <c r="Y50" s="2"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
-      <c r="AB50" s="3"/>
-      <c r="AC50" s="3"/>
-      <c r="AD50" s="3"/>
-      <c r="AE50" s="3"/>
-      <c r="AF50" s="3"/>
-      <c r="AG50" s="3"/>
-      <c r="AH50" s="3"/>
-      <c r="AI50" s="3"/>
-      <c r="AJ50" s="3"/>
-      <c r="AK50" s="3"/>
-      <c r="AL50" s="3"/>
-      <c r="AM50" s="3"/>
-      <c r="AN50" s="3"/>
-      <c r="AO50" s="3"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1"/>
+      <c r="AL50" s="1"/>
+      <c r="AM50" s="1"/>
+      <c r="AN50" s="1"/>
+      <c r="AO50" s="1"/>
     </row>
     <row r="51" spans="1:41">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="3"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -4021,39 +4331,39 @@
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
       <c r="Y51" s="2"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
-      <c r="AB51" s="3"/>
-      <c r="AC51" s="3"/>
-      <c r="AD51" s="3"/>
-      <c r="AE51" s="3"/>
-      <c r="AF51" s="3"/>
-      <c r="AG51" s="3"/>
-      <c r="AH51" s="3"/>
-      <c r="AI51" s="3"/>
-      <c r="AJ51" s="3"/>
-      <c r="AK51" s="3"/>
-      <c r="AL51" s="3"/>
-      <c r="AM51" s="3"/>
-      <c r="AN51" s="3"/>
-      <c r="AO51" s="3"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AH51" s="1"/>
+      <c r="AI51" s="1"/>
+      <c r="AJ51" s="1"/>
+      <c r="AK51" s="1"/>
+      <c r="AL51" s="1"/>
+      <c r="AM51" s="1"/>
+      <c r="AN51" s="1"/>
+      <c r="AO51" s="1"/>
     </row>
     <row r="52" spans="1:41">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="3"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -4065,39 +4375,39 @@
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
       <c r="Y52" s="2"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
-      <c r="AB52" s="3"/>
-      <c r="AC52" s="3"/>
-      <c r="AD52" s="3"/>
-      <c r="AE52" s="3"/>
-      <c r="AF52" s="3"/>
-      <c r="AG52" s="3"/>
-      <c r="AH52" s="3"/>
-      <c r="AI52" s="3"/>
-      <c r="AJ52" s="3"/>
-      <c r="AK52" s="3"/>
-      <c r="AL52" s="3"/>
-      <c r="AM52" s="3"/>
-      <c r="AN52" s="3"/>
-      <c r="AO52" s="3"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
+      <c r="AG52" s="1"/>
+      <c r="AH52" s="1"/>
+      <c r="AI52" s="1"/>
+      <c r="AJ52" s="1"/>
+      <c r="AK52" s="1"/>
+      <c r="AL52" s="1"/>
+      <c r="AM52" s="1"/>
+      <c r="AN52" s="1"/>
+      <c r="AO52" s="1"/>
     </row>
     <row r="53" spans="1:41">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="3"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -4109,39 +4419,39 @@
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
       <c r="Y53" s="2"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="3"/>
-      <c r="AB53" s="3"/>
-      <c r="AC53" s="3"/>
-      <c r="AD53" s="3"/>
-      <c r="AE53" s="3"/>
-      <c r="AF53" s="3"/>
-      <c r="AG53" s="3"/>
-      <c r="AH53" s="3"/>
-      <c r="AI53" s="3"/>
-      <c r="AJ53" s="3"/>
-      <c r="AK53" s="3"/>
-      <c r="AL53" s="3"/>
-      <c r="AM53" s="3"/>
-      <c r="AN53" s="3"/>
-      <c r="AO53" s="3"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="1"/>
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AF53" s="1"/>
+      <c r="AG53" s="1"/>
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1"/>
+      <c r="AJ53" s="1"/>
+      <c r="AK53" s="1"/>
+      <c r="AL53" s="1"/>
+      <c r="AM53" s="1"/>
+      <c r="AN53" s="1"/>
+      <c r="AO53" s="1"/>
     </row>
     <row r="54" spans="1:41">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="3"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -4153,39 +4463,39 @@
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
       <c r="Y54" s="2"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
-      <c r="AB54" s="3"/>
-      <c r="AC54" s="3"/>
-      <c r="AD54" s="3"/>
-      <c r="AE54" s="3"/>
-      <c r="AF54" s="3"/>
-      <c r="AG54" s="3"/>
-      <c r="AH54" s="3"/>
-      <c r="AI54" s="3"/>
-      <c r="AJ54" s="3"/>
-      <c r="AK54" s="3"/>
-      <c r="AL54" s="3"/>
-      <c r="AM54" s="3"/>
-      <c r="AN54" s="3"/>
-      <c r="AO54" s="3"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1"/>
+      <c r="AG54" s="1"/>
+      <c r="AH54" s="1"/>
+      <c r="AI54" s="1"/>
+      <c r="AJ54" s="1"/>
+      <c r="AK54" s="1"/>
+      <c r="AL54" s="1"/>
+      <c r="AM54" s="1"/>
+      <c r="AN54" s="1"/>
+      <c r="AO54" s="1"/>
     </row>
     <row r="55" spans="1:41">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="J55" s="3"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -4197,39 +4507,39 @@
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
       <c r="Y55" s="2"/>
-      <c r="Z55" s="3"/>
-      <c r="AA55" s="3"/>
-      <c r="AB55" s="3"/>
-      <c r="AC55" s="3"/>
-      <c r="AD55" s="3"/>
-      <c r="AE55" s="3"/>
-      <c r="AF55" s="3"/>
-      <c r="AG55" s="3"/>
-      <c r="AH55" s="3"/>
-      <c r="AI55" s="3"/>
-      <c r="AJ55" s="3"/>
-      <c r="AK55" s="3"/>
-      <c r="AL55" s="3"/>
-      <c r="AM55" s="3"/>
-      <c r="AN55" s="3"/>
-      <c r="AO55" s="3"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+      <c r="AC55" s="1"/>
+      <c r="AD55" s="1"/>
+      <c r="AE55" s="1"/>
+      <c r="AF55" s="1"/>
+      <c r="AG55" s="1"/>
+      <c r="AH55" s="1"/>
+      <c r="AI55" s="1"/>
+      <c r="AJ55" s="1"/>
+      <c r="AK55" s="1"/>
+      <c r="AL55" s="1"/>
+      <c r="AM55" s="1"/>
+      <c r="AN55" s="1"/>
+      <c r="AO55" s="1"/>
     </row>
     <row r="56" spans="1:41">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="J56" s="3"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -4241,39 +4551,39 @@
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
       <c r="Y56" s="2"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="3"/>
-      <c r="AB56" s="3"/>
-      <c r="AC56" s="3"/>
-      <c r="AD56" s="3"/>
-      <c r="AE56" s="3"/>
-      <c r="AF56" s="3"/>
-      <c r="AG56" s="3"/>
-      <c r="AH56" s="3"/>
-      <c r="AI56" s="3"/>
-      <c r="AJ56" s="3"/>
-      <c r="AK56" s="3"/>
-      <c r="AL56" s="3"/>
-      <c r="AM56" s="3"/>
-      <c r="AN56" s="3"/>
-      <c r="AO56" s="3"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+      <c r="AC56" s="1"/>
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AF56" s="1"/>
+      <c r="AG56" s="1"/>
+      <c r="AH56" s="1"/>
+      <c r="AI56" s="1"/>
+      <c r="AJ56" s="1"/>
+      <c r="AK56" s="1"/>
+      <c r="AL56" s="1"/>
+      <c r="AM56" s="1"/>
+      <c r="AN56" s="1"/>
+      <c r="AO56" s="1"/>
     </row>
     <row r="57" spans="1:41">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-      <c r="J57" s="3"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -4285,39 +4595,39 @@
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
-      <c r="AB57" s="3"/>
-      <c r="AC57" s="3"/>
-      <c r="AD57" s="3"/>
-      <c r="AE57" s="3"/>
-      <c r="AF57" s="3"/>
-      <c r="AG57" s="3"/>
-      <c r="AH57" s="3"/>
-      <c r="AI57" s="3"/>
-      <c r="AJ57" s="3"/>
-      <c r="AK57" s="3"/>
-      <c r="AL57" s="3"/>
-      <c r="AM57" s="3"/>
-      <c r="AN57" s="3"/>
-      <c r="AO57" s="3"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+      <c r="AC57" s="1"/>
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AF57" s="1"/>
+      <c r="AG57" s="1"/>
+      <c r="AH57" s="1"/>
+      <c r="AI57" s="1"/>
+      <c r="AJ57" s="1"/>
+      <c r="AK57" s="1"/>
+      <c r="AL57" s="1"/>
+      <c r="AM57" s="1"/>
+      <c r="AN57" s="1"/>
+      <c r="AO57" s="1"/>
     </row>
     <row r="58" spans="1:41">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
-      <c r="J58" s="3"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -4329,39 +4639,39 @@
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
       <c r="Y58" s="2"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="3"/>
-      <c r="AB58" s="3"/>
-      <c r="AC58" s="3"/>
-      <c r="AD58" s="3"/>
-      <c r="AE58" s="3"/>
-      <c r="AF58" s="3"/>
-      <c r="AG58" s="3"/>
-      <c r="AH58" s="3"/>
-      <c r="AI58" s="3"/>
-      <c r="AJ58" s="3"/>
-      <c r="AK58" s="3"/>
-      <c r="AL58" s="3"/>
-      <c r="AM58" s="3"/>
-      <c r="AN58" s="3"/>
-      <c r="AO58" s="3"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
+      <c r="AC58" s="1"/>
+      <c r="AD58" s="1"/>
+      <c r="AE58" s="1"/>
+      <c r="AF58" s="1"/>
+      <c r="AG58" s="1"/>
+      <c r="AH58" s="1"/>
+      <c r="AI58" s="1"/>
+      <c r="AJ58" s="1"/>
+      <c r="AK58" s="1"/>
+      <c r="AL58" s="1"/>
+      <c r="AM58" s="1"/>
+      <c r="AN58" s="1"/>
+      <c r="AO58" s="1"/>
     </row>
     <row r="59" spans="1:41">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
-      <c r="J59" s="3"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -4373,39 +4683,39 @@
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
       <c r="Y59" s="2"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
-      <c r="AB59" s="3"/>
-      <c r="AC59" s="3"/>
-      <c r="AD59" s="3"/>
-      <c r="AE59" s="3"/>
-      <c r="AF59" s="3"/>
-      <c r="AG59" s="3"/>
-      <c r="AH59" s="3"/>
-      <c r="AI59" s="3"/>
-      <c r="AJ59" s="3"/>
-      <c r="AK59" s="3"/>
-      <c r="AL59" s="3"/>
-      <c r="AM59" s="3"/>
-      <c r="AN59" s="3"/>
-      <c r="AO59" s="3"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+      <c r="AB59" s="1"/>
+      <c r="AC59" s="1"/>
+      <c r="AD59" s="1"/>
+      <c r="AE59" s="1"/>
+      <c r="AF59" s="1"/>
+      <c r="AG59" s="1"/>
+      <c r="AH59" s="1"/>
+      <c r="AI59" s="1"/>
+      <c r="AJ59" s="1"/>
+      <c r="AK59" s="1"/>
+      <c r="AL59" s="1"/>
+      <c r="AM59" s="1"/>
+      <c r="AN59" s="1"/>
+      <c r="AO59" s="1"/>
     </row>
     <row r="60" spans="1:41">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-      <c r="J60" s="3"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -4417,39 +4727,39 @@
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
       <c r="Y60" s="2"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
-      <c r="AB60" s="3"/>
-      <c r="AC60" s="3"/>
-      <c r="AD60" s="3"/>
-      <c r="AE60" s="3"/>
-      <c r="AF60" s="3"/>
-      <c r="AG60" s="3"/>
-      <c r="AH60" s="3"/>
-      <c r="AI60" s="3"/>
-      <c r="AJ60" s="3"/>
-      <c r="AK60" s="3"/>
-      <c r="AL60" s="3"/>
-      <c r="AM60" s="3"/>
-      <c r="AN60" s="3"/>
-      <c r="AO60" s="3"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1"/>
+      <c r="AC60" s="1"/>
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AF60" s="1"/>
+      <c r="AG60" s="1"/>
+      <c r="AH60" s="1"/>
+      <c r="AI60" s="1"/>
+      <c r="AJ60" s="1"/>
+      <c r="AK60" s="1"/>
+      <c r="AL60" s="1"/>
+      <c r="AM60" s="1"/>
+      <c r="AN60" s="1"/>
+      <c r="AO60" s="1"/>
     </row>
     <row r="61" spans="1:41">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="3"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -4461,39 +4771,39 @@
       <c r="W61" s="2"/>
       <c r="X61" s="2"/>
       <c r="Y61" s="2"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
-      <c r="AB61" s="3"/>
-      <c r="AC61" s="3"/>
-      <c r="AD61" s="3"/>
-      <c r="AE61" s="3"/>
-      <c r="AF61" s="3"/>
-      <c r="AG61" s="3"/>
-      <c r="AH61" s="3"/>
-      <c r="AI61" s="3"/>
-      <c r="AJ61" s="3"/>
-      <c r="AK61" s="3"/>
-      <c r="AL61" s="3"/>
-      <c r="AM61" s="3"/>
-      <c r="AN61" s="3"/>
-      <c r="AO61" s="3"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
+      <c r="AC61" s="1"/>
+      <c r="AD61" s="1"/>
+      <c r="AE61" s="1"/>
+      <c r="AF61" s="1"/>
+      <c r="AG61" s="1"/>
+      <c r="AH61" s="1"/>
+      <c r="AI61" s="1"/>
+      <c r="AJ61" s="1"/>
+      <c r="AK61" s="1"/>
+      <c r="AL61" s="1"/>
+      <c r="AM61" s="1"/>
+      <c r="AN61" s="1"/>
+      <c r="AO61" s="1"/>
     </row>
     <row r="62" spans="1:41">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
-      <c r="J62" s="3"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -4505,39 +4815,39 @@
       <c r="W62" s="2"/>
       <c r="X62" s="2"/>
       <c r="Y62" s="2"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
-      <c r="AB62" s="3"/>
-      <c r="AC62" s="3"/>
-      <c r="AD62" s="3"/>
-      <c r="AE62" s="3"/>
-      <c r="AF62" s="3"/>
-      <c r="AG62" s="3"/>
-      <c r="AH62" s="3"/>
-      <c r="AI62" s="3"/>
-      <c r="AJ62" s="3"/>
-      <c r="AK62" s="3"/>
-      <c r="AL62" s="3"/>
-      <c r="AM62" s="3"/>
-      <c r="AN62" s="3"/>
-      <c r="AO62" s="3"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+      <c r="AC62" s="1"/>
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="1"/>
+      <c r="AF62" s="1"/>
+      <c r="AG62" s="1"/>
+      <c r="AH62" s="1"/>
+      <c r="AI62" s="1"/>
+      <c r="AJ62" s="1"/>
+      <c r="AK62" s="1"/>
+      <c r="AL62" s="1"/>
+      <c r="AM62" s="1"/>
+      <c r="AN62" s="1"/>
+      <c r="AO62" s="1"/>
     </row>
     <row r="63" spans="1:41">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-      <c r="J63" s="3"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -4549,39 +4859,39 @@
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
       <c r="Y63" s="2"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
-      <c r="AB63" s="3"/>
-      <c r="AC63" s="3"/>
-      <c r="AD63" s="3"/>
-      <c r="AE63" s="3"/>
-      <c r="AF63" s="3"/>
-      <c r="AG63" s="3"/>
-      <c r="AH63" s="3"/>
-      <c r="AI63" s="3"/>
-      <c r="AJ63" s="3"/>
-      <c r="AK63" s="3"/>
-      <c r="AL63" s="3"/>
-      <c r="AM63" s="3"/>
-      <c r="AN63" s="3"/>
-      <c r="AO63" s="3"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+      <c r="AB63" s="1"/>
+      <c r="AC63" s="1"/>
+      <c r="AD63" s="1"/>
+      <c r="AE63" s="1"/>
+      <c r="AF63" s="1"/>
+      <c r="AG63" s="1"/>
+      <c r="AH63" s="1"/>
+      <c r="AI63" s="1"/>
+      <c r="AJ63" s="1"/>
+      <c r="AK63" s="1"/>
+      <c r="AL63" s="1"/>
+      <c r="AM63" s="1"/>
+      <c r="AN63" s="1"/>
+      <c r="AO63" s="1"/>
     </row>
     <row r="64" spans="1:41">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="3"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -4593,39 +4903,39 @@
       <c r="W64" s="2"/>
       <c r="X64" s="2"/>
       <c r="Y64" s="2"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
-      <c r="AB64" s="3"/>
-      <c r="AC64" s="3"/>
-      <c r="AD64" s="3"/>
-      <c r="AE64" s="3"/>
-      <c r="AF64" s="3"/>
-      <c r="AG64" s="3"/>
-      <c r="AH64" s="3"/>
-      <c r="AI64" s="3"/>
-      <c r="AJ64" s="3"/>
-      <c r="AK64" s="3"/>
-      <c r="AL64" s="3"/>
-      <c r="AM64" s="3"/>
-      <c r="AN64" s="3"/>
-      <c r="AO64" s="3"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
+      <c r="AC64" s="1"/>
+      <c r="AD64" s="1"/>
+      <c r="AE64" s="1"/>
+      <c r="AF64" s="1"/>
+      <c r="AG64" s="1"/>
+      <c r="AH64" s="1"/>
+      <c r="AI64" s="1"/>
+      <c r="AJ64" s="1"/>
+      <c r="AK64" s="1"/>
+      <c r="AL64" s="1"/>
+      <c r="AM64" s="1"/>
+      <c r="AN64" s="1"/>
+      <c r="AO64" s="1"/>
     </row>
     <row r="65" spans="1:41">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-      <c r="J65" s="3"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -4637,39 +4947,39 @@
       <c r="W65" s="2"/>
       <c r="X65" s="2"/>
       <c r="Y65" s="2"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
-      <c r="AB65" s="3"/>
-      <c r="AC65" s="3"/>
-      <c r="AD65" s="3"/>
-      <c r="AE65" s="3"/>
-      <c r="AF65" s="3"/>
-      <c r="AG65" s="3"/>
-      <c r="AH65" s="3"/>
-      <c r="AI65" s="3"/>
-      <c r="AJ65" s="3"/>
-      <c r="AK65" s="3"/>
-      <c r="AL65" s="3"/>
-      <c r="AM65" s="3"/>
-      <c r="AN65" s="3"/>
-      <c r="AO65" s="3"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+      <c r="AB65" s="1"/>
+      <c r="AC65" s="1"/>
+      <c r="AD65" s="1"/>
+      <c r="AE65" s="1"/>
+      <c r="AF65" s="1"/>
+      <c r="AG65" s="1"/>
+      <c r="AH65" s="1"/>
+      <c r="AI65" s="1"/>
+      <c r="AJ65" s="1"/>
+      <c r="AK65" s="1"/>
+      <c r="AL65" s="1"/>
+      <c r="AM65" s="1"/>
+      <c r="AN65" s="1"/>
+      <c r="AO65" s="1"/>
     </row>
     <row r="66" spans="1:41">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="3"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -4681,39 +4991,39 @@
       <c r="W66" s="2"/>
       <c r="X66" s="2"/>
       <c r="Y66" s="2"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
-      <c r="AB66" s="3"/>
-      <c r="AC66" s="3"/>
-      <c r="AD66" s="3"/>
-      <c r="AE66" s="3"/>
-      <c r="AF66" s="3"/>
-      <c r="AG66" s="3"/>
-      <c r="AH66" s="3"/>
-      <c r="AI66" s="3"/>
-      <c r="AJ66" s="3"/>
-      <c r="AK66" s="3"/>
-      <c r="AL66" s="3"/>
-      <c r="AM66" s="3"/>
-      <c r="AN66" s="3"/>
-      <c r="AO66" s="3"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
+      <c r="AC66" s="1"/>
+      <c r="AD66" s="1"/>
+      <c r="AE66" s="1"/>
+      <c r="AF66" s="1"/>
+      <c r="AG66" s="1"/>
+      <c r="AH66" s="1"/>
+      <c r="AI66" s="1"/>
+      <c r="AJ66" s="1"/>
+      <c r="AK66" s="1"/>
+      <c r="AL66" s="1"/>
+      <c r="AM66" s="1"/>
+      <c r="AN66" s="1"/>
+      <c r="AO66" s="1"/>
     </row>
     <row r="67" spans="1:41">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="3"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -4725,39 +5035,39 @@
       <c r="W67" s="2"/>
       <c r="X67" s="2"/>
       <c r="Y67" s="2"/>
-      <c r="Z67" s="3"/>
-      <c r="AA67" s="3"/>
-      <c r="AB67" s="3"/>
-      <c r="AC67" s="3"/>
-      <c r="AD67" s="3"/>
-      <c r="AE67" s="3"/>
-      <c r="AF67" s="3"/>
-      <c r="AG67" s="3"/>
-      <c r="AH67" s="3"/>
-      <c r="AI67" s="3"/>
-      <c r="AJ67" s="3"/>
-      <c r="AK67" s="3"/>
-      <c r="AL67" s="3"/>
-      <c r="AM67" s="3"/>
-      <c r="AN67" s="3"/>
-      <c r="AO67" s="3"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
+      <c r="AC67" s="1"/>
+      <c r="AD67" s="1"/>
+      <c r="AE67" s="1"/>
+      <c r="AF67" s="1"/>
+      <c r="AG67" s="1"/>
+      <c r="AH67" s="1"/>
+      <c r="AI67" s="1"/>
+      <c r="AJ67" s="1"/>
+      <c r="AK67" s="1"/>
+      <c r="AL67" s="1"/>
+      <c r="AM67" s="1"/>
+      <c r="AN67" s="1"/>
+      <c r="AO67" s="1"/>
     </row>
     <row r="68" spans="1:41">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
-      <c r="J68" s="3"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -4769,39 +5079,39 @@
       <c r="W68" s="2"/>
       <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
-      <c r="Z68" s="3"/>
-      <c r="AA68" s="3"/>
-      <c r="AB68" s="3"/>
-      <c r="AC68" s="3"/>
-      <c r="AD68" s="3"/>
-      <c r="AE68" s="3"/>
-      <c r="AF68" s="3"/>
-      <c r="AG68" s="3"/>
-      <c r="AH68" s="3"/>
-      <c r="AI68" s="3"/>
-      <c r="AJ68" s="3"/>
-      <c r="AK68" s="3"/>
-      <c r="AL68" s="3"/>
-      <c r="AM68" s="3"/>
-      <c r="AN68" s="3"/>
-      <c r="AO68" s="3"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
+      <c r="AC68" s="1"/>
+      <c r="AD68" s="1"/>
+      <c r="AE68" s="1"/>
+      <c r="AF68" s="1"/>
+      <c r="AG68" s="1"/>
+      <c r="AH68" s="1"/>
+      <c r="AI68" s="1"/>
+      <c r="AJ68" s="1"/>
+      <c r="AK68" s="1"/>
+      <c r="AL68" s="1"/>
+      <c r="AM68" s="1"/>
+      <c r="AN68" s="1"/>
+      <c r="AO68" s="1"/>
     </row>
     <row r="69" spans="1:41">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
-      <c r="J69" s="3"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -4813,1156 +5123,1156 @@
       <c r="W69" s="2"/>
       <c r="X69" s="2"/>
       <c r="Y69" s="2"/>
-      <c r="Z69" s="3"/>
-      <c r="AA69" s="3"/>
-      <c r="AB69" s="3"/>
-      <c r="AC69" s="3"/>
-      <c r="AD69" s="3"/>
-      <c r="AE69" s="3"/>
-      <c r="AF69" s="3"/>
-      <c r="AG69" s="3"/>
-      <c r="AH69" s="3"/>
-      <c r="AI69" s="3"/>
-      <c r="AJ69" s="3"/>
-      <c r="AK69" s="3"/>
-      <c r="AL69" s="3"/>
-      <c r="AM69" s="3"/>
-      <c r="AN69" s="3"/>
-      <c r="AO69" s="3"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+      <c r="AB69" s="1"/>
+      <c r="AC69" s="1"/>
+      <c r="AD69" s="1"/>
+      <c r="AE69" s="1"/>
+      <c r="AF69" s="1"/>
+      <c r="AG69" s="1"/>
+      <c r="AH69" s="1"/>
+      <c r="AI69" s="1"/>
+      <c r="AJ69" s="1"/>
+      <c r="AK69" s="1"/>
+      <c r="AL69" s="1"/>
+      <c r="AM69" s="1"/>
+      <c r="AN69" s="1"/>
+      <c r="AO69" s="1"/>
     </row>
     <row r="70" spans="1:37">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="AJ70" s="3"/>
-      <c r="AK70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="AJ70" s="1"/>
+      <c r="AK70" s="1"/>
     </row>
     <row r="71" spans="1:37">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="AJ71" s="3"/>
-      <c r="AK71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="AJ71" s="1"/>
+      <c r="AK71" s="1"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="1"/>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
-      <c r="E138" s="1"/>
-      <c r="F138" s="1"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-      <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-      <c r="E142" s="1"/>
-      <c r="F142" s="1"/>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="1"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-      <c r="E143" s="1"/>
-      <c r="F143" s="1"/>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-      <c r="E144" s="1"/>
-      <c r="F144" s="1"/>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="1"/>
-      <c r="B147" s="1"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="1"/>
-      <c r="B150" s="1"/>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="1"/>
-      <c r="B157" s="1"/>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
     </row>
     <row r="160" spans="2:4">
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
     </row>
     <row r="161" spans="2:4">
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
     </row>
     <row r="162" spans="2:4">
-      <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
     </row>
     <row r="163" spans="2:4">
-      <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
     </row>
     <row r="164" spans="2:4">
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
     </row>
     <row r="165" spans="2:4">
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
     </row>
     <row r="166" spans="2:4">
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
     </row>
     <row r="167" spans="2:4">
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
     </row>
     <row r="168" spans="2:4">
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
     </row>
     <row r="169" spans="2:4">
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
     </row>
     <row r="170" spans="2:4">
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
     </row>
     <row r="171" spans="2:4">
-      <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
     </row>
     <row r="172" spans="2:4">
-      <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
     </row>
     <row r="173" spans="2:4">
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
     </row>
     <row r="174" spans="2:4">
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
     </row>
     <row r="175" spans="2:4">
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
     </row>
     <row r="176" spans="2:4">
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
     </row>
     <row r="177" spans="2:4">
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
     </row>
     <row r="178" spans="2:4">
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
     </row>
     <row r="179" spans="2:4">
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
     </row>
     <row r="180" spans="2:4">
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
     </row>
     <row r="181" spans="2:4">
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
     </row>
     <row r="182" spans="2:4">
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
     </row>
     <row r="183" spans="2:4">
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
     </row>
     <row r="184" spans="2:4">
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
     </row>
     <row r="185" spans="2:4">
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
     </row>
     <row r="186" spans="2:4">
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
     </row>
     <row r="187" spans="2:4">
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
     </row>
     <row r="188" spans="2:4">
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
     </row>
     <row r="189" spans="2:4">
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
     </row>
     <row r="190" spans="2:4">
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
     </row>
     <row r="191" spans="2:4">
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
     </row>
     <row r="192" spans="2:4">
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
     </row>
     <row r="193" spans="2:4">
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
     </row>
     <row r="194" spans="2:4">
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
     </row>
     <row r="195" spans="2:4">
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
     </row>
     <row r="196" spans="2:4">
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
     </row>
     <row r="197" spans="2:4">
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
     </row>
     <row r="198" spans="2:4">
-      <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
     </row>
     <row r="199" spans="2:4">
-      <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
     </row>
     <row r="200" spans="2:4">
-      <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
     </row>
     <row r="201" spans="2:4">
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
     </row>
     <row r="202" spans="2:4">
-      <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
     </row>
     <row r="203" spans="2:4">
-      <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
     </row>
     <row r="204" spans="2:4">
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
     </row>
     <row r="205" spans="2:4">
-      <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
     </row>
     <row r="206" spans="2:4">
-      <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
     </row>
     <row r="207" spans="2:4">
-      <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
     </row>
     <row r="208" spans="2:4">
-      <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
     </row>
     <row r="209" spans="2:4">
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
     </row>
     <row r="210" spans="2:4">
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
     </row>
     <row r="211" spans="2:4">
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
     </row>
     <row r="212" spans="2:4">
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="B212" s="3"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
     </row>
     <row r="213" spans="2:4">
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
     </row>
     <row r="214" spans="2:4">
-      <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
     </row>
     <row r="215" spans="2:4">
-      <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
     </row>
     <row r="216" spans="2:4">
-      <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
     </row>
     <row r="217" spans="2:4">
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="B217" s="3"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
     </row>
     <row r="218" spans="2:4">
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="B218" s="3"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
     </row>
     <row r="219" spans="2:4">
-      <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="B219" s="3"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
     </row>
     <row r="220" spans="2:4">
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
     </row>
     <row r="221" spans="2:4">
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
     </row>
     <row r="222" spans="2:4">
-      <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
     </row>
     <row r="223" spans="2:4">
-      <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
     </row>
     <row r="224" spans="2:4">
-      <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
+      <c r="B224" s="3"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
     </row>
     <row r="225" spans="2:4">
-      <c r="B225" s="1"/>
-      <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
+      <c r="B225" s="3"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3"/>
     </row>
     <row r="226" spans="2:4">
-      <c r="B226" s="1"/>
-      <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
     </row>
     <row r="227" spans="2:4">
-      <c r="B227" s="1"/>
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
+      <c r="B227" s="3"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3"/>
     </row>
     <row r="228" spans="2:4">
-      <c r="B228" s="1"/>
-      <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
     </row>
     <row r="229" spans="2:4">
-      <c r="B229" s="1"/>
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
     </row>
     <row r="230" spans="2:4">
-      <c r="B230" s="1"/>
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
     </row>
     <row r="231" spans="2:4">
-      <c r="B231" s="1"/>
-      <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3"/>
     </row>
     <row r="232" spans="2:4">
-      <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
     </row>
     <row r="233" spans="2:4">
-      <c r="B233" s="1"/>
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
     </row>
     <row r="234" spans="2:4">
-      <c r="B234" s="1"/>
-      <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
+      <c r="B234" s="3"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
     </row>
     <row r="235" spans="2:4">
-      <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
     </row>
     <row r="236" spans="2:4">
-      <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
     </row>
     <row r="237" spans="2:4">
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
     </row>
     <row r="238" spans="2:4">
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
+      <c r="B238" s="3"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
     </row>
     <row r="239" spans="2:4">
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
     </row>
     <row r="240" spans="2:4">
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -5991,156 +6301,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6166,375 +6476,375 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B48" t="s">
@@ -6542,7 +6852,7 @@
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>225</v>
       </c>
       <c r="B49" t="s">
@@ -6550,7 +6860,7 @@
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="3" t="s">
         <v>227</v>
       </c>
       <c r="B50" t="s">
@@ -6558,7 +6868,7 @@
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>229</v>
       </c>
       <c r="B51" t="s">
@@ -6566,7 +6876,7 @@
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="3" t="s">
         <v>231</v>
       </c>
       <c r="B52" t="s">
@@ -6574,7 +6884,7 @@
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>233</v>
       </c>
       <c r="B53" t="s">
@@ -6582,7 +6892,7 @@
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B54" t="s">
@@ -6590,7 +6900,7 @@
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>237</v>
       </c>
       <c r="B55" t="s">
@@ -6598,7 +6908,7 @@
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="3" t="s">
         <v>239</v>
       </c>
       <c r="B56" t="s">
@@ -6606,7 +6916,7 @@
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>241</v>
       </c>
       <c r="B57" t="s">
@@ -6614,7 +6924,7 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="3" t="s">
         <v>243</v>
       </c>
       <c r="B58" t="s">
@@ -6622,7 +6932,7 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>245</v>
       </c>
       <c r="B59" t="s">
@@ -6630,7 +6940,7 @@
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B60" t="s">
@@ -6638,12 +6948,887 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B61" t="s">
         <v>250</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="39.0833333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1666666666667" customWidth="1"/>
+    <col min="3" max="3" width="36.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
